--- a/AERA_1.2_WD_Requirement_Register.xlsx
+++ b/AERA_1.2_WD_Requirement_Register.xlsx
@@ -1,12 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="1" r:id="R988878c27e38483f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applicability Template" sheetId="2" r:id="Rdfef0a0599f042e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="3" r:id="Raa34a5b278cc4f85"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Requirements" sheetId="1" r:id="Rdbf5de4c56314608"/>
+    <sheet name="Applicability Template" sheetId="2" r:id="R64b9a5696c234fe4"/>
+    <sheet name="Control" sheetId="3" r:id="Rf0048aba29754b6c"/>
+  </sheets>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8546,7 +8547,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8678d6790444c58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6b1669cd95745e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14604,7 +14605,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f57cc9e29744f4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d5a5d16680b4e27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14672,10 +14673,10 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="103" t="str">
-        <x:v>Controlled date</x:v>
+        <x:v>Build ID</x:v>
       </x:c>
       <x:c r="B6" s="104" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>AERA-001-1.2WD-20260807.1</x:v>
       </x:c>
       <x:c r="D6" t="str">
         <x:v>Proposed requirements</x:v>
@@ -14687,10 +14688,10 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="103" t="str">
-        <x:v>Author / owner</x:v>
+        <x:v>Controlled date</x:v>
       </x:c>
       <x:c r="B7" s="104" t="str">
-        <x:v>Angelis Pseftis / independent author</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="D7" t="str">
         <x:v>Governance-family requirements</x:v>
@@ -14702,10 +14703,10 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="103" t="str">
-        <x:v>Status</x:v>
+        <x:v>Author / owner</x:v>
       </x:c>
       <x:c r="B8" s="104" t="str">
-        <x:v>Working Draft; independently authored; no NIST endorsement or support claim</x:v>
+        <x:v>Angelis Pseftis / independent author</x:v>
       </x:c>
       <x:c r="D8" t="str">
         <x:v>Applicability records</x:v>
@@ -14717,10 +14718,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="103" t="str">
-        <x:v>Source rule</x:v>
+        <x:v>Status</x:v>
       </x:c>
       <x:c r="B9" s="104" t="str">
-        <x:v>Generated from the same controlled source used for the master specification</x:v>
+        <x:v>Working Draft; independently authored; no NIST endorsement or support claim</x:v>
       </x:c>
       <x:c r="D9" t="str">
         <x:v>Applicability set</x:v>
@@ -14731,12 +14732,26 @@
       </x:c>
     </x:row>
     <x:row r="10">
+      <x:c r="A10" s="103" t="str">
+        <x:v>Public snapshot</x:v>
+      </x:c>
+      <x:c r="B10" s="104" t="str">
+        <x:v>2026-08-08; https://github.com/redxking/AERA; formal public review not open</x:v>
+      </x:c>
       <x:c r="D10" t="str">
         <x:v>Applicability QA ready</x:v>
       </x:c>
       <x:c r="E10" t="n">
         <x:f>COUNTIF('Applicability Template'!O2:O200,"READY")</x:f>
         <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="103" t="str">
+        <x:v>Source rule</x:v>
+      </x:c>
+      <x:c r="B11" s="104" t="str">
+        <x:v>Generated from the same controlled source used for the master specification</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
